--- a/data_lake/datos_diarios_preliminares/dt=2026-07-22/Temp-max-julio-26.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-07-22/Temp-max-julio-26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\02. Datos Diarios\Tablas\Datos hidrometeorologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91272F23-ED52-4EC4-8664-C93F4ABDA1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAA1DAB-7C34-475F-82BE-558340007586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TMAX_PRINCIPALES_CIUDADES" sheetId="1" r:id="rId1"/>
@@ -9484,7 +9484,9 @@
       <c r="X5" s="57">
         <v>29.2</v>
       </c>
-      <c r="Y5" s="57"/>
+      <c r="Y5" s="57">
+        <v>30.8</v>
+      </c>
       <c r="Z5" s="57"/>
       <c r="AA5" s="57"/>
       <c r="AB5" s="57"/>
@@ -9497,7 +9499,7 @@
       <c r="AI5" s="57"/>
       <c r="AJ5" s="37">
         <f>+IF(SUM($E5:$AI5)&gt;0,LOOKUP(1000,$E5:$AI5),NA())</f>
-        <v>29.2</v>
+        <v>30.8</v>
       </c>
       <c r="AK5" s="21">
         <f>+MAX($E5:$AI5)</f>
@@ -9515,11 +9517,11 @@
       </c>
       <c r="AO5" s="23">
         <f>IF(COUNTIF(E5:AI5,"&gt;0")&gt;=15,AVERAGE(E5:AI5),"")</f>
-        <v>31.090000000000003</v>
+        <v>31.076190476190476</v>
       </c>
       <c r="AP5" s="23">
         <f>IF(AN5&gt;0,IFERROR(AO5-AN5,""),"")</f>
-        <v>0.89262822399177466</v>
+        <v>0.87881870018224717</v>
       </c>
     </row>
     <row r="6" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9595,7 +9597,9 @@
       <c r="X6" s="57">
         <v>29.7</v>
       </c>
-      <c r="Y6" s="57"/>
+      <c r="Y6" s="57">
+        <v>30.8</v>
+      </c>
       <c r="Z6" s="57"/>
       <c r="AA6" s="57"/>
       <c r="AB6" s="57"/>
@@ -9608,7 +9612,7 @@
       <c r="AI6" s="57"/>
       <c r="AJ6" s="37">
         <f t="shared" ref="AJ6:AJ48" si="0">+IF(SUM($E6:$AI6)&gt;0,LOOKUP(1000,$E6:$AI6),NA())</f>
-        <v>29.7</v>
+        <v>30.8</v>
       </c>
       <c r="AK6" s="21">
         <f t="shared" ref="AK6:AK48" si="1">+MAX($E6:$AI6)</f>
@@ -9626,11 +9630,11 @@
       </c>
       <c r="AO6" s="23">
         <f t="shared" ref="AO6:AO15" si="3">IF(COUNTIF(E6:AI6,"&gt;0")&gt;=15,AVERAGE(E6:AI6),"")</f>
-        <v>30.614999999999998</v>
+        <v>30.62380952380952</v>
       </c>
       <c r="AP6" s="23">
         <f t="shared" ref="AP6:AP48" si="4">IF(AN6&gt;0,IFERROR(AO6-AN6,""),"")</f>
-        <v>-3.9280397022341873E-2</v>
+        <v>-3.0470873212820493E-2</v>
       </c>
     </row>
     <row r="7" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9706,7 +9710,9 @@
       <c r="X7" s="57">
         <v>30.6</v>
       </c>
-      <c r="Y7" s="57"/>
+      <c r="Y7" s="57">
+        <v>32.6</v>
+      </c>
       <c r="Z7" s="57"/>
       <c r="AA7" s="57"/>
       <c r="AB7" s="57"/>
@@ -9719,7 +9725,7 @@
       <c r="AI7" s="57"/>
       <c r="AJ7" s="37">
         <f t="shared" si="0"/>
-        <v>30.6</v>
+        <v>32.6</v>
       </c>
       <c r="AK7" s="21">
         <f t="shared" si="1"/>
@@ -9737,11 +9743,11 @@
       </c>
       <c r="AO7" s="23">
         <f t="shared" si="3"/>
-        <v>35.89</v>
+        <v>35.733333333333334</v>
       </c>
       <c r="AP7" s="23">
         <f t="shared" si="4"/>
-        <v>2.523983992430928</v>
+        <v>2.3673173257642617</v>
       </c>
     </row>
     <row r="8" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9817,7 +9823,9 @@
       <c r="X8" s="57">
         <v>30.2</v>
       </c>
-      <c r="Y8" s="57"/>
+      <c r="Y8" s="57">
+        <v>32.799999999999997</v>
+      </c>
       <c r="Z8" s="57"/>
       <c r="AA8" s="57"/>
       <c r="AB8" s="57"/>
@@ -9830,7 +9838,7 @@
       <c r="AI8" s="57"/>
       <c r="AJ8" s="37">
         <f t="shared" si="0"/>
-        <v>30.2</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="AK8" s="21">
         <f t="shared" si="1"/>
@@ -9848,11 +9856,11 @@
       </c>
       <c r="AO8" s="23">
         <f t="shared" si="3"/>
-        <v>33.270000000000003</v>
+        <v>33.247619047619047</v>
       </c>
       <c r="AP8" s="23">
         <f t="shared" si="4"/>
-        <v>1.0209569892473098</v>
+        <v>0.99857603686635343</v>
       </c>
     </row>
     <row r="9" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9928,7 +9936,9 @@
       <c r="X9" s="57">
         <v>30.4</v>
       </c>
-      <c r="Y9" s="57"/>
+      <c r="Y9" s="57">
+        <v>34</v>
+      </c>
       <c r="Z9" s="57"/>
       <c r="AA9" s="57"/>
       <c r="AB9" s="57"/>
@@ -9941,7 +9951,7 @@
       <c r="AI9" s="57"/>
       <c r="AJ9" s="37">
         <f t="shared" si="0"/>
-        <v>30.4</v>
+        <v>34</v>
       </c>
       <c r="AK9" s="21">
         <f t="shared" si="1"/>
@@ -9959,11 +9969,11 @@
       </c>
       <c r="AO9" s="23">
         <f t="shared" si="3"/>
-        <v>33.774999999999999</v>
+        <v>33.785714285714285</v>
       </c>
       <c r="AP9" s="23">
         <f t="shared" si="4"/>
-        <v>0.68375386231615209</v>
+        <v>0.69446814803043821</v>
       </c>
     </row>
     <row r="10" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10039,7 +10049,9 @@
       <c r="X10" s="57">
         <v>35.5</v>
       </c>
-      <c r="Y10" s="57"/>
+      <c r="Y10" s="57">
+        <v>35.799999999999997</v>
+      </c>
       <c r="Z10" s="57"/>
       <c r="AA10" s="57"/>
       <c r="AB10" s="57"/>
@@ -10052,7 +10064,7 @@
       <c r="AI10" s="57"/>
       <c r="AJ10" s="37">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="AK10" s="21">
         <f t="shared" si="1"/>
@@ -10070,11 +10082,11 @@
       </c>
       <c r="AO10" s="23">
         <f t="shared" si="3"/>
-        <v>35.784999999999997</v>
+        <v>35.785714285714278</v>
       </c>
       <c r="AP10" s="23">
         <f t="shared" si="4"/>
-        <v>0.40476177233963995</v>
+        <v>0.40547605805392095</v>
       </c>
     </row>
     <row r="11" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10150,7 +10162,9 @@
       <c r="X11" s="57">
         <v>36.4</v>
       </c>
-      <c r="Y11" s="57"/>
+      <c r="Y11" s="57">
+        <v>37.4</v>
+      </c>
       <c r="Z11" s="57"/>
       <c r="AA11" s="57"/>
       <c r="AB11" s="57"/>
@@ -10163,7 +10177,7 @@
       <c r="AI11" s="57"/>
       <c r="AJ11" s="37">
         <f t="shared" si="0"/>
-        <v>36.4</v>
+        <v>37.4</v>
       </c>
       <c r="AK11" s="21">
         <f t="shared" si="1"/>
@@ -10181,11 +10195,11 @@
       </c>
       <c r="AO11" s="23">
         <f t="shared" si="3"/>
-        <v>38.184999999999988</v>
+        <v>38.147619047619038</v>
       </c>
       <c r="AP11" s="23">
         <f t="shared" si="4"/>
-        <v>2.6477159071513867</v>
+        <v>2.6103349547704369</v>
       </c>
     </row>
     <row r="12" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10261,7 +10275,9 @@
       <c r="X12" s="57">
         <v>30.4</v>
       </c>
-      <c r="Y12" s="57"/>
+      <c r="Y12" s="57">
+        <v>33.4</v>
+      </c>
       <c r="Z12" s="57"/>
       <c r="AA12" s="57"/>
       <c r="AB12" s="57"/>
@@ -10274,7 +10290,7 @@
       <c r="AI12" s="57"/>
       <c r="AJ12" s="37">
         <f t="shared" si="0"/>
-        <v>30.4</v>
+        <v>33.4</v>
       </c>
       <c r="AK12" s="21">
         <f t="shared" si="1"/>
@@ -10292,11 +10308,11 @@
       </c>
       <c r="AO12" s="23">
         <f t="shared" si="3"/>
-        <v>34.739999999999995</v>
+        <v>34.67619047619047</v>
       </c>
       <c r="AP12" s="23">
         <f t="shared" si="4"/>
-        <v>2.5513758538262579</v>
+        <v>2.4875663300167332</v>
       </c>
     </row>
     <row r="13" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10372,7 +10388,9 @@
       <c r="X13" s="57">
         <v>31.2</v>
       </c>
-      <c r="Y13" s="57"/>
+      <c r="Y13" s="57">
+        <v>33.799999999999997</v>
+      </c>
       <c r="Z13" s="57"/>
       <c r="AA13" s="57"/>
       <c r="AB13" s="57"/>
@@ -10385,7 +10403,7 @@
       <c r="AI13" s="57"/>
       <c r="AJ13" s="37">
         <f t="shared" si="0"/>
-        <v>31.2</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="AK13" s="21">
         <f t="shared" si="1"/>
@@ -10403,11 +10421,11 @@
       </c>
       <c r="AO13" s="23">
         <f t="shared" si="3"/>
-        <v>35.96</v>
+        <v>35.857142857142854</v>
       </c>
       <c r="AP13" s="23">
         <f t="shared" si="4"/>
-        <v>2.5782078853046642</v>
+        <v>2.4753507424475174</v>
       </c>
     </row>
     <row r="14" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10483,7 +10501,9 @@
       <c r="X14" s="57">
         <v>31.1</v>
       </c>
-      <c r="Y14" s="57"/>
+      <c r="Y14" s="57">
+        <v>34.9</v>
+      </c>
       <c r="Z14" s="57"/>
       <c r="AA14" s="57"/>
       <c r="AB14" s="57"/>
@@ -10496,7 +10516,7 @@
       <c r="AI14" s="57"/>
       <c r="AJ14" s="37">
         <f t="shared" si="0"/>
-        <v>31.1</v>
+        <v>34.9</v>
       </c>
       <c r="AK14" s="21">
         <f t="shared" si="1"/>
@@ -10514,11 +10534,11 @@
       </c>
       <c r="AO14" s="23">
         <f t="shared" si="3"/>
-        <v>35.049999999999997</v>
+        <v>35.042857142857144</v>
       </c>
       <c r="AP14" s="23">
         <f t="shared" si="4"/>
-        <v>1.8250634007857656</v>
+        <v>1.8179205436429129</v>
       </c>
     </row>
     <row r="15" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10594,7 +10614,9 @@
       <c r="X15" s="57">
         <v>31.5</v>
       </c>
-      <c r="Y15" s="57"/>
+      <c r="Y15" s="57">
+        <v>31.9</v>
+      </c>
       <c r="Z15" s="57"/>
       <c r="AA15" s="57"/>
       <c r="AB15" s="57"/>
@@ -10607,7 +10629,7 @@
       <c r="AI15" s="57"/>
       <c r="AJ15" s="37">
         <f t="shared" si="0"/>
-        <v>31.5</v>
+        <v>31.9</v>
       </c>
       <c r="AK15" s="21">
         <f t="shared" si="1"/>
@@ -10625,11 +10647,11 @@
       </c>
       <c r="AO15" s="23">
         <f t="shared" si="3"/>
-        <v>31.82</v>
+        <v>31.823809523809523</v>
       </c>
       <c r="AP15" s="23">
         <f t="shared" si="4"/>
-        <v>8.4662543920050126E-2</v>
+        <v>8.8472067729572501E-2</v>
       </c>
     </row>
     <row r="16" spans="1:46" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10754,7 +10776,9 @@
       <c r="X17" s="57">
         <v>31</v>
       </c>
-      <c r="Y17" s="57"/>
+      <c r="Y17" s="57">
+        <v>31.6</v>
+      </c>
       <c r="Z17" s="57"/>
       <c r="AA17" s="57"/>
       <c r="AB17" s="57"/>
@@ -10767,7 +10791,7 @@
       <c r="AI17" s="57"/>
       <c r="AJ17" s="37">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>31.6</v>
       </c>
       <c r="AK17" s="21">
         <f t="shared" si="1"/>
@@ -10785,11 +10809,11 @@
       </c>
       <c r="AO17" s="23">
         <f>IF(COUNTIF(E17:AI17,"&gt;0")&gt;=15,AVERAGE(E17:AI17),"")</f>
-        <v>34.439999999999991</v>
+        <v>34.304761904761897</v>
       </c>
       <c r="AP17" s="23">
         <f>IF(AN17&gt;0,IFERROR(AO17-AN17,""),"")</f>
-        <v>1.7660177975528342</v>
+        <v>1.6307797023147401</v>
       </c>
     </row>
     <row r="18" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10865,7 +10889,9 @@
       <c r="X18" s="57">
         <v>24.8</v>
       </c>
-      <c r="Y18" s="57"/>
+      <c r="Y18" s="57">
+        <v>25.9</v>
+      </c>
       <c r="Z18" s="57"/>
       <c r="AA18" s="57"/>
       <c r="AB18" s="57"/>
@@ -10878,7 +10904,7 @@
       <c r="AI18" s="57"/>
       <c r="AJ18" s="37">
         <f t="shared" si="0"/>
-        <v>24.8</v>
+        <v>25.9</v>
       </c>
       <c r="AK18" s="21">
         <f t="shared" si="1"/>
@@ -10896,11 +10922,11 @@
       </c>
       <c r="AO18" s="23">
         <f t="shared" ref="AO18:AO33" si="5">IF(COUNTIF(E18:AI18,"&gt;0")&gt;=15,AVERAGE(E18:AI18),"")</f>
-        <v>27.970000000000006</v>
+        <v>27.871428571428574</v>
       </c>
       <c r="AP18" s="23">
         <f t="shared" si="4"/>
-        <v>1.9101291460431362</v>
+        <v>1.8115577174717039</v>
       </c>
     </row>
     <row r="19" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10976,7 +11002,9 @@
       <c r="X19" s="57">
         <v>29.8</v>
       </c>
-      <c r="Y19" s="57"/>
+      <c r="Y19" s="57">
+        <v>33.700000000000003</v>
+      </c>
       <c r="Z19" s="57"/>
       <c r="AA19" s="57"/>
       <c r="AB19" s="57"/>
@@ -10989,7 +11017,7 @@
       <c r="AI19" s="57"/>
       <c r="AJ19" s="37">
         <f t="shared" si="0"/>
-        <v>29.8</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="AK19" s="21">
         <f t="shared" si="1"/>
@@ -11007,11 +11035,11 @@
       </c>
       <c r="AO19" s="23">
         <f t="shared" si="5"/>
-        <v>33.584999999999994</v>
+        <v>33.590476190476188</v>
       </c>
       <c r="AP19" s="23">
         <f t="shared" si="4"/>
-        <v>0.33403759733035088</v>
+        <v>0.33951378780654551</v>
       </c>
     </row>
     <row r="20" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11087,7 +11115,9 @@
       <c r="X20" s="57">
         <v>26.9</v>
       </c>
-      <c r="Y20" s="57"/>
+      <c r="Y20" s="57">
+        <v>31.2</v>
+      </c>
       <c r="Z20" s="57"/>
       <c r="AA20" s="57"/>
       <c r="AB20" s="57"/>
@@ -11100,7 +11130,7 @@
       <c r="AI20" s="57"/>
       <c r="AJ20" s="37">
         <f t="shared" si="0"/>
-        <v>26.9</v>
+        <v>31.2</v>
       </c>
       <c r="AK20" s="21">
         <f t="shared" si="1"/>
@@ -11118,11 +11148,11 @@
       </c>
       <c r="AO20" s="23">
         <f t="shared" si="5"/>
-        <v>30.385000000000002</v>
+        <v>30.423809523809528</v>
       </c>
       <c r="AP20" s="23">
         <f t="shared" si="4"/>
-        <v>1.7441954022988533</v>
+        <v>1.7830049261083794</v>
       </c>
     </row>
     <row r="21" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11198,7 +11228,9 @@
       <c r="X21" s="57">
         <v>21.9</v>
       </c>
-      <c r="Y21" s="57"/>
+      <c r="Y21" s="57">
+        <v>24.4</v>
+      </c>
       <c r="Z21" s="57"/>
       <c r="AA21" s="57"/>
       <c r="AB21" s="57"/>
@@ -11211,7 +11243,7 @@
       <c r="AI21" s="57"/>
       <c r="AJ21" s="37">
         <f t="shared" si="0"/>
-        <v>21.9</v>
+        <v>24.4</v>
       </c>
       <c r="AK21" s="21">
         <f t="shared" si="1"/>
@@ -11229,11 +11261,11 @@
       </c>
       <c r="AO21" s="23">
         <f t="shared" si="5"/>
-        <v>24.289999999999996</v>
+        <v>24.295238095238091</v>
       </c>
       <c r="AP21" s="23">
         <f t="shared" si="4"/>
-        <v>1.6804968483500247</v>
+        <v>1.6857349435881197</v>
       </c>
     </row>
     <row r="22" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11377,7 +11409,9 @@
       <c r="X23" s="57">
         <v>27.2</v>
       </c>
-      <c r="Y23" s="57"/>
+      <c r="Y23" s="57">
+        <v>29.2</v>
+      </c>
       <c r="Z23" s="57"/>
       <c r="AA23" s="57"/>
       <c r="AB23" s="57"/>
@@ -11390,7 +11424,7 @@
       <c r="AI23" s="57"/>
       <c r="AJ23" s="37">
         <f t="shared" si="0"/>
-        <v>27.2</v>
+        <v>29.2</v>
       </c>
       <c r="AK23" s="21">
         <f t="shared" si="1"/>
@@ -11408,11 +11442,11 @@
       </c>
       <c r="AO23" s="23">
         <f t="shared" si="5"/>
-        <v>28.645000000000003</v>
+        <v>28.671428571428578</v>
       </c>
       <c r="AP23" s="23">
         <f t="shared" si="4"/>
-        <v>1.7766129032258036</v>
+        <v>1.8030414746543784</v>
       </c>
     </row>
     <row r="24" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11488,7 +11522,9 @@
       <c r="X24" s="57">
         <v>27.7</v>
       </c>
-      <c r="Y24" s="57"/>
+      <c r="Y24" s="57">
+        <v>28.5</v>
+      </c>
       <c r="Z24" s="57"/>
       <c r="AA24" s="57"/>
       <c r="AB24" s="57"/>
@@ -11501,7 +11537,7 @@
       <c r="AI24" s="57"/>
       <c r="AJ24" s="37">
         <f t="shared" si="0"/>
-        <v>27.7</v>
+        <v>28.5</v>
       </c>
       <c r="AK24" s="21">
         <f t="shared" si="1"/>
@@ -11519,11 +11555,11 @@
       </c>
       <c r="AO24" s="23">
         <f t="shared" si="5"/>
-        <v>29.685000000000002</v>
+        <v>29.62857142857143</v>
       </c>
       <c r="AP24" s="23">
         <f t="shared" si="4"/>
-        <v>1.4331758832565207</v>
+        <v>1.3767473118279483</v>
       </c>
     </row>
     <row r="25" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11599,7 +11635,9 @@
       <c r="X25" s="57">
         <v>32.4</v>
       </c>
-      <c r="Y25" s="57"/>
+      <c r="Y25" s="57">
+        <v>32.799999999999997</v>
+      </c>
       <c r="Z25" s="57"/>
       <c r="AA25" s="57"/>
       <c r="AB25" s="57"/>
@@ -11612,7 +11650,7 @@
       <c r="AI25" s="57"/>
       <c r="AJ25" s="37">
         <f t="shared" si="0"/>
-        <v>32.4</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="AK25" s="21">
         <f t="shared" si="1"/>
@@ -11630,11 +11668,11 @@
       </c>
       <c r="AO25" s="23">
         <f t="shared" si="5"/>
-        <v>32.25500000000001</v>
+        <v>32.280952380952385</v>
       </c>
       <c r="AP25" s="23">
         <f t="shared" si="4"/>
-        <v>1.8791346067789405</v>
+        <v>1.9050869877313161</v>
       </c>
     </row>
     <row r="26" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11710,7 +11748,9 @@
       <c r="X26" s="57">
         <v>19.399999999999999</v>
       </c>
-      <c r="Y26" s="57"/>
+      <c r="Y26" s="57">
+        <v>20.3</v>
+      </c>
       <c r="Z26" s="57"/>
       <c r="AA26" s="57"/>
       <c r="AB26" s="57"/>
@@ -11723,7 +11763,7 @@
       <c r="AI26" s="57"/>
       <c r="AJ26" s="37">
         <f t="shared" si="0"/>
-        <v>19.399999999999999</v>
+        <v>20.3</v>
       </c>
       <c r="AK26" s="21">
         <f t="shared" si="1"/>
@@ -11741,11 +11781,11 @@
       </c>
       <c r="AO26" s="23">
         <f t="shared" si="5"/>
-        <v>19.650000000000002</v>
+        <v>19.680952380952384</v>
       </c>
       <c r="AP26" s="23">
         <f t="shared" si="4"/>
-        <v>1.1071283925566426</v>
+        <v>1.1380807735090244</v>
       </c>
     </row>
     <row r="27" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11821,7 +11861,9 @@
       <c r="X27" s="57">
         <v>20</v>
       </c>
-      <c r="Y27" s="57"/>
+      <c r="Y27" s="57">
+        <v>19.600000000000001</v>
+      </c>
       <c r="Z27" s="57"/>
       <c r="AA27" s="57"/>
       <c r="AB27" s="57"/>
@@ -11834,7 +11876,7 @@
       <c r="AI27" s="57"/>
       <c r="AJ27" s="37">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="AK27" s="21">
         <f t="shared" si="1"/>
@@ -11852,11 +11894,11 @@
       </c>
       <c r="AO27" s="23">
         <f t="shared" si="5"/>
-        <v>18.674999999999997</v>
+        <v>18.719047619047618</v>
       </c>
       <c r="AP27" s="23">
         <f t="shared" si="4"/>
-        <v>1.9929494558916083</v>
+        <v>2.0369970749392294</v>
       </c>
     </row>
     <row r="28" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11932,7 +11974,9 @@
       <c r="X28" s="57">
         <v>30.5</v>
       </c>
-      <c r="Y28" s="57"/>
+      <c r="Y28" s="57">
+        <v>32.1</v>
+      </c>
       <c r="Z28" s="57"/>
       <c r="AA28" s="57"/>
       <c r="AB28" s="57"/>
@@ -11945,7 +11989,7 @@
       <c r="AI28" s="57"/>
       <c r="AJ28" s="37">
         <f t="shared" si="0"/>
-        <v>30.5</v>
+        <v>32.1</v>
       </c>
       <c r="AK28" s="21">
         <f t="shared" si="1"/>
@@ -11963,11 +12007,11 @@
       </c>
       <c r="AO28" s="23">
         <f t="shared" si="5"/>
-        <v>31.895000000000003</v>
+        <v>31.904761904761909</v>
       </c>
       <c r="AP28" s="23">
         <f t="shared" si="4"/>
-        <v>1.3665473983438439</v>
+        <v>1.3763093031057494</v>
       </c>
     </row>
     <row r="29" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12109,7 +12153,9 @@
       <c r="X30" s="57">
         <v>35.299999999999997</v>
       </c>
-      <c r="Y30" s="57"/>
+      <c r="Y30" s="57">
+        <v>36.5</v>
+      </c>
       <c r="Z30" s="57"/>
       <c r="AA30" s="57"/>
       <c r="AB30" s="57"/>
@@ -12122,7 +12168,7 @@
       <c r="AI30" s="57"/>
       <c r="AJ30" s="37">
         <f t="shared" si="0"/>
-        <v>35.299999999999997</v>
+        <v>36.5</v>
       </c>
       <c r="AK30" s="21">
         <f t="shared" si="1"/>
@@ -12140,11 +12186,11 @@
       </c>
       <c r="AO30" s="23">
         <f t="shared" si="5"/>
-        <v>34.540000000000006</v>
+        <v>34.63333333333334</v>
       </c>
       <c r="AP30" s="23">
         <f t="shared" si="4"/>
-        <v>0.79774910394265675</v>
+        <v>0.89108243727599046</v>
       </c>
     </row>
     <row r="31" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12220,7 +12266,9 @@
       <c r="X31" s="57">
         <v>24.9</v>
       </c>
-      <c r="Y31" s="57"/>
+      <c r="Y31" s="57">
+        <v>24.9</v>
+      </c>
       <c r="Z31" s="57"/>
       <c r="AA31" s="57"/>
       <c r="AB31" s="57"/>
@@ -12251,11 +12299,11 @@
       </c>
       <c r="AO31" s="23">
         <f t="shared" si="5"/>
-        <v>27.409999999999997</v>
+        <v>27.290476190476188</v>
       </c>
       <c r="AP31" s="23">
         <f t="shared" si="4"/>
-        <v>2.0225751628793773</v>
+        <v>1.9030513533555684</v>
       </c>
     </row>
     <row r="32" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12331,7 +12379,9 @@
       <c r="X32" s="57">
         <v>19.399999999999999</v>
       </c>
-      <c r="Y32" s="57"/>
+      <c r="Y32" s="57">
+        <v>19.600000000000001</v>
+      </c>
       <c r="Z32" s="57"/>
       <c r="AA32" s="57"/>
       <c r="AB32" s="57"/>
@@ -12344,7 +12394,7 @@
       <c r="AI32" s="57"/>
       <c r="AJ32" s="37">
         <f t="shared" si="0"/>
-        <v>19.399999999999999</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="AK32" s="21">
         <f t="shared" si="1"/>
@@ -12362,11 +12412,11 @@
       </c>
       <c r="AO32" s="23">
         <f t="shared" si="5"/>
-        <v>17.940000000000001</v>
+        <v>18.019047619047619</v>
       </c>
       <c r="AP32" s="23">
         <f t="shared" si="4"/>
-        <v>1.6104622267387505</v>
+        <v>1.6895098457863682</v>
       </c>
     </row>
     <row r="33" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12442,7 +12492,9 @@
       <c r="X33" s="57">
         <v>17.399999999999999</v>
       </c>
-      <c r="Y33" s="57"/>
+      <c r="Y33" s="57">
+        <v>16.600000000000001</v>
+      </c>
       <c r="Z33" s="57"/>
       <c r="AA33" s="57"/>
       <c r="AB33" s="57"/>
@@ -12455,7 +12507,7 @@
       <c r="AI33" s="57"/>
       <c r="AJ33" s="37">
         <f t="shared" si="0"/>
-        <v>17.399999999999999</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="AK33" s="21">
         <f t="shared" si="1"/>
@@ -12473,11 +12525,11 @@
       </c>
       <c r="AO33" s="23">
         <f t="shared" si="5"/>
-        <v>15.754999999999999</v>
+        <v>15.795238095238094</v>
       </c>
       <c r="AP33" s="23">
         <f t="shared" si="4"/>
-        <v>1.0103874675565496</v>
+        <v>1.0506255627946448</v>
       </c>
       <c r="AT33" s="15"/>
     </row>
@@ -12605,7 +12657,9 @@
       <c r="X35" s="57">
         <v>31.4</v>
       </c>
-      <c r="Y35" s="57"/>
+      <c r="Y35" s="57">
+        <v>31.2</v>
+      </c>
       <c r="Z35" s="57"/>
       <c r="AA35" s="57"/>
       <c r="AB35" s="57"/>
@@ -12618,7 +12672,7 @@
       <c r="AI35" s="57"/>
       <c r="AJ35" s="37">
         <f t="shared" si="0"/>
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="AK35" s="21">
         <f t="shared" si="1"/>
@@ -12636,11 +12690,11 @@
       </c>
       <c r="AO35" s="23">
         <f>IF(COUNTIF(E35:AI35,"&gt;0")&gt;=15,AVERAGE(E35:AI35),"")</f>
-        <v>31.989999999999991</v>
+        <v>31.952380952380945</v>
       </c>
       <c r="AP35" s="23">
         <f t="shared" si="4"/>
-        <v>0.91730414746542976</v>
+        <v>0.87968509984638388</v>
       </c>
       <c r="AT35" s="15"/>
     </row>
@@ -12837,7 +12891,9 @@
       <c r="X38" s="57">
         <v>26.4</v>
       </c>
-      <c r="Y38" s="57"/>
+      <c r="Y38" s="57">
+        <v>31.6</v>
+      </c>
       <c r="Z38" s="57"/>
       <c r="AA38" s="57"/>
       <c r="AB38" s="57"/>
@@ -12850,7 +12906,7 @@
       <c r="AI38" s="57"/>
       <c r="AJ38" s="37">
         <f t="shared" si="0"/>
-        <v>26.4</v>
+        <v>31.6</v>
       </c>
       <c r="AK38" s="21">
         <f t="shared" si="1"/>
@@ -12868,11 +12924,11 @@
       </c>
       <c r="AO38" s="23">
         <f>IF(COUNTIF(E38:AI38,"&gt;0")&gt;=15,AVERAGE(E38:AI38),"")</f>
-        <v>30.044999999999995</v>
+        <v>30.119047619047613</v>
       </c>
       <c r="AP38" s="23">
         <f t="shared" si="4"/>
-        <v>1.5973776607413726E-2</v>
+        <v>9.0021395655032421E-2</v>
       </c>
       <c r="AT38" s="15"/>
     </row>
@@ -12949,7 +13005,9 @@
       <c r="X39" s="57">
         <v>32.4</v>
       </c>
-      <c r="Y39" s="57"/>
+      <c r="Y39" s="57">
+        <v>33.1</v>
+      </c>
       <c r="Z39" s="57"/>
       <c r="AA39" s="57"/>
       <c r="AB39" s="57"/>
@@ -12962,7 +13020,7 @@
       <c r="AI39" s="57"/>
       <c r="AJ39" s="37">
         <f t="shared" si="0"/>
-        <v>32.4</v>
+        <v>33.1</v>
       </c>
       <c r="AK39" s="21">
         <f t="shared" si="1"/>
@@ -12980,11 +13038,11 @@
       </c>
       <c r="AO39" s="23">
         <f t="shared" ref="AO39:AO48" si="7">IF(COUNTIF(E39:AI39,"&gt;0")&gt;=15,AVERAGE(E39:AI39),"")</f>
-        <v>31.27</v>
+        <v>31.357142857142858</v>
       </c>
       <c r="AP39" s="23">
         <f t="shared" si="4"/>
-        <v>0.42686688913607895</v>
+        <v>0.51400974627893703</v>
       </c>
       <c r="AT39" s="15"/>
     </row>
@@ -13061,7 +13119,9 @@
       <c r="X40" s="57">
         <v>30.8</v>
       </c>
-      <c r="Y40" s="57"/>
+      <c r="Y40" s="57">
+        <v>31.3</v>
+      </c>
       <c r="Z40" s="57"/>
       <c r="AA40" s="57"/>
       <c r="AB40" s="57"/>
@@ -13074,7 +13134,7 @@
       <c r="AI40" s="57"/>
       <c r="AJ40" s="37">
         <f t="shared" si="0"/>
-        <v>30.8</v>
+        <v>31.3</v>
       </c>
       <c r="AK40" s="21">
         <f t="shared" si="1"/>
@@ -13092,11 +13152,11 @@
       </c>
       <c r="AO40" s="23">
         <f t="shared" si="7"/>
-        <v>29.540000000000003</v>
+        <v>29.623809523809523</v>
       </c>
       <c r="AP40" s="23">
         <f t="shared" si="4"/>
-        <v>0.59245161290322201</v>
+        <v>0.67626113671274268</v>
       </c>
       <c r="AT40" s="15"/>
     </row>
@@ -13173,7 +13233,9 @@
       <c r="X41" s="57">
         <v>29.6</v>
       </c>
-      <c r="Y41" s="57"/>
+      <c r="Y41" s="57">
+        <v>32.6</v>
+      </c>
       <c r="Z41" s="57"/>
       <c r="AA41" s="57"/>
       <c r="AB41" s="57"/>
@@ -13186,7 +13248,7 @@
       <c r="AI41" s="57"/>
       <c r="AJ41" s="37">
         <f t="shared" si="0"/>
-        <v>29.6</v>
+        <v>32.6</v>
       </c>
       <c r="AK41" s="21">
         <f t="shared" si="1"/>
@@ -13204,11 +13266,11 @@
       </c>
       <c r="AO41" s="23">
         <f t="shared" si="7"/>
-        <v>30.350000000000005</v>
+        <v>30.457142857142863</v>
       </c>
       <c r="AP41" s="23">
         <f t="shared" si="4"/>
-        <v>0.9836917562724139</v>
+        <v>1.0908346134152715</v>
       </c>
       <c r="AT41" s="15"/>
     </row>
@@ -13346,7 +13408,9 @@
       <c r="X43" s="57">
         <v>32.200000000000003</v>
       </c>
-      <c r="Y43" s="57"/>
+      <c r="Y43" s="57">
+        <v>33</v>
+      </c>
       <c r="Z43" s="57"/>
       <c r="AA43" s="57"/>
       <c r="AB43" s="57"/>
@@ -13359,7 +13423,7 @@
       <c r="AI43" s="57"/>
       <c r="AJ43" s="37">
         <f t="shared" si="0"/>
-        <v>32.200000000000003</v>
+        <v>33</v>
       </c>
       <c r="AK43" s="21">
         <f t="shared" si="1"/>
@@ -13377,11 +13441,11 @@
       </c>
       <c r="AO43" s="23">
         <f t="shared" si="7"/>
-        <v>30.788235294117644</v>
+        <v>30.911111111111111</v>
       </c>
       <c r="AP43" s="23">
         <f t="shared" si="4"/>
-        <v>0.7271734661606537</v>
+        <v>0.85004928315412087</v>
       </c>
       <c r="AT43" s="15"/>
     </row>
@@ -13456,7 +13520,9 @@
       <c r="X44" s="29">
         <v>31.4</v>
       </c>
-      <c r="Y44" s="29"/>
+      <c r="Y44" s="29">
+        <v>30.4</v>
+      </c>
       <c r="Z44" s="29"/>
       <c r="AA44" s="29"/>
       <c r="AB44" s="29"/>
@@ -13469,7 +13535,7 @@
       <c r="AI44" s="57"/>
       <c r="AJ44" s="37">
         <f t="shared" si="0"/>
-        <v>31.4</v>
+        <v>30.4</v>
       </c>
       <c r="AK44" s="21">
         <f t="shared" si="1"/>
@@ -13487,11 +13553,11 @@
       </c>
       <c r="AO44" s="23">
         <f t="shared" si="7"/>
-        <v>31.178947368421046</v>
+        <v>31.139999999999993</v>
       </c>
       <c r="AP44" s="23">
         <f t="shared" si="4"/>
-        <v>2.1357601630605849</v>
+        <v>2.0968127946395327</v>
       </c>
       <c r="AT44" s="15"/>
     </row>
@@ -13568,7 +13634,9 @@
       <c r="X45" s="57">
         <v>31.6</v>
       </c>
-      <c r="Y45" s="57"/>
+      <c r="Y45" s="57">
+        <v>31.6</v>
+      </c>
       <c r="Z45" s="57"/>
       <c r="AA45" s="57"/>
       <c r="AB45" s="57"/>
@@ -13599,11 +13667,11 @@
       </c>
       <c r="AO45" s="23">
         <f t="shared" si="7"/>
-        <v>30.310000000000009</v>
+        <v>30.371428571428581</v>
       </c>
       <c r="AP45" s="23">
         <f t="shared" si="4"/>
-        <v>0.76418360712117916</v>
+        <v>0.82561217854975055</v>
       </c>
       <c r="AT45" s="15"/>
     </row>
@@ -13819,7 +13887,9 @@
       <c r="X48" s="57">
         <v>32.299999999999997</v>
       </c>
-      <c r="Y48" s="57"/>
+      <c r="Y48" s="57">
+        <v>32.799999999999997</v>
+      </c>
       <c r="Z48" s="57"/>
       <c r="AA48" s="57"/>
       <c r="AB48" s="57"/>
@@ -13832,7 +13902,7 @@
       <c r="AI48" s="57"/>
       <c r="AJ48" s="37">
         <f t="shared" si="0"/>
-        <v>32.299999999999997</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="AK48" s="21">
         <f t="shared" si="1"/>
@@ -13850,11 +13920,11 @@
       </c>
       <c r="AO48" s="23">
         <f t="shared" si="7"/>
-        <v>30.494999999999997</v>
+        <v>30.604761904761901</v>
       </c>
       <c r="AP48" s="23">
         <f t="shared" si="4"/>
-        <v>0.15246714456391786</v>
+        <v>0.26222904932582125</v>
       </c>
     </row>
     <row r="49" spans="5:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
